--- a/stories/arbres/ATOM-FAM.VER.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara est dans le jardin avec papa. Elle arrose les fleurs. L'arrosoir est lourd. L'eau fait un bruit doux. Le pot de basilic bascule. La terre s'étale. Sara sent son visage chaud. Elle va vers papa. Sara dit : papa, le pot est tombé. C'est moi. Papa l'écoute. Papa dit : merci de raconter. On ramasse la terre. Les mains sont un peu sales. Plus tard, dans la cuisine, Sara touche un verre. Le verre tremble. Sara pense : je peux raconter à papa ou maman. Elle dit : maman, j'ai touché le verre. Il a bougé. Maman dit : merci Sara. Raconter aide, au jardin et à la maison. Papa et maman sont là.</t>
+          <t>Sara est dans le jardin avec papa. Elle arrose les fleurs. L'arrosoir est lourd. L'eau fait un bruit doux. Le pot de basilic bascule. La terre s'étale. Sara sent son visage chaud. Elle va vers papa. Papa, le pot est tombé. C'est moi. Papa l'écoute. Merci de raconter. On ramasse la terre. Les mains sont un peu sales. Plus tard, dans la cuisine, Sara touche un verre. Le verre tremble. Sara pense : je peux raconter à papa ou maman. Maman, j'ai touché le verre. Il a bougé. Merci Sara. Raconter aide, au jardin et à la maison. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara est dans le jardin avec papa. Elle arrose les fleurs. L'arrosoir est lourd. L'eau fait un bruit doux. Le pot de basilic bascule. La terre s'étale. Sara sent son visage chaud. Elle va vers papa.
+enfant-f|Papa, le pot est tombé. C'est moi. Papa l'écoute.
+papa|Merci de raconter. On ramasse la terre.
+narrateur|Les mains sont un peu sales. Plus tard, dans la cuisine, Sara touche un verre. Le verre tremble. Sara pense : je peux raconter à papa ou maman.
+narrateur|Maman, j'ai touché le verre. Il a bougé.
+maman|Merci Sara. Raconter aide, au jardin et à la maison. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Quelque chose est tombé. Que fait Sara ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a raconté au jardin. Puis elle a raconté dans la cuisine. Papa et maman écoutent. Raconter, c'est possible à chaque fois.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le basilic est remis. Le verre est stable. Sara se lave les mains.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 maman|Merci Sara. Raconter aide, au jardin et à la maison. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Quelque chose est tombé. Que fait Sara ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Sara a raconté au jardin. Puis elle a raconté dans la cuisine. Papa et maman écoutent. Raconter, c'est possible à chaque fois.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Le basilic est remis. Le verre est stable. Sara se lave les mains.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.VER.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sara raconte à papa et maman</t>
+          <t>Victorina raconte à papa et maman</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Au jardin, le pot de basilic bascule. Victorina raconte à papa. Plus tard, un verre bouge. Elle raconte à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara est dans le jardin avec papa. Elle arrose les fleurs. L'arrosoir est lourd. L'eau fait un bruit doux. Le pot de basilic bascule. La terre s'étale. Sara sent son visage chaud. Elle va vers papa. Papa, le pot est tombé. C'est moi. Papa l'écoute. Merci de raconter. On ramasse la terre. Les mains sont un peu sales. Plus tard, dans la cuisine, Sara touche un verre. Le verre tremble. Sara pense : je peux raconter à papa ou maman. Maman, j'ai touché le verre. Il a bougé. Merci Sara. Raconter aide, au jardin et à la maison. Papa et maman sont là.</t>
+          <t>L'arrosoir laisse une goutte sur les dalles. La goutte brille, puis s'étale. Le basilic sent fort, tout vert. Une coccinelle marche sur une feuille. La terre est sombre et un peu froide. Les mains de papa sont humides. Un seau jaune attend près des fleurs. Tu as vu la coccinelle, Victorina ? Oui, papa. Elle est toute petite. Elle a des points noirs. Tu veux arroser un peu ? Oui. L'arrosoir est lourd. En ce moment, Victorina arrose les fleurs. L'eau fait un bruit doux. Elle veut déplacer le pot de basilic. Le pot bascule. La terre s'étale. Ça fait un tas brun sur la dalle. Victorina sent son visage chaud. Elle a le ventre serré. Elle va vers papa. Papa, le pot est tombé. C'est moi. Je t'écoute. Merci de raconter. On ramasse la terre. Tu as fait du bon travail. Tu veux la petite pelle ? Oui, papa. Les mains sont un peu sales. La terre revient dans le pot. Le basilic se redresse, tout penché. On se lave les mains, après ? Oui. Plus tard, la cuisine sent le thym. Un verre d'eau attend sur la table. Victorina touche le verre. Le verre tremble. Victorina pense. Je peux raconter à papa ou maman. Maman essuie une assiette. Maman, j'ai touché le verre. Il a bougé. Je t'écoute, Victorina. Merci de raconter. Raconter aide, au jardin et à la maison. On raconte à papa ou maman. Bravo. C'est du bon travail. Tu veux que je tienne le verre avec toi ? Oui, maman. Le verre redevient calme. Victorina souffle. Les mains sont propres, maintenant ? Oui, papa. J'ai raconté deux fois. Oui. Chaque fois, on raconte. Tu veux sentir le basilic, encore ? Oui. Il sent fort. Victorina se lave un peu les doigts. L'eau est froide, puis tiède.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,78 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sara est dans le jardin avec papa. Elle arrose les fleurs. L'arrosoir est lourd. L'eau fait un bruit doux. Le pot de basilic bascule. La terre s'étale. Sara sent son visage chaud. Elle va vers papa.
-enfant-f|Papa, le pot est tombé. C'est moi. Papa l'écoute.
-papa|Merci de raconter. On ramasse la terre.
-narrateur|Les mains sont un peu sales. Plus tard, dans la cuisine, Sara touche un verre. Le verre tremble. Sara pense : je peux raconter à papa ou maman.
-narrateur|Maman, j'ai touché le verre. Il a bougé.
-maman|Merci Sara. Raconter aide, au jardin et à la maison. Papa et maman sont là.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|L'arrosoir laisse une goutte sur les dalles.
+narrateur|La goutte brille, puis s'étale.
+narrateur|Le basilic sent fort, tout vert.
+narrateur|Une coccinelle marche sur une feuille.
+narrateur|La terre est sombre et un peu froide.
+narrateur|Les mains de papa sont humides.
+narrateur|Un seau jaune attend près des fleurs.
+papa|Tu as vu la coccinelle, Victorina ?
+enfant-f|Oui, papa.
+enfant-f|Elle est toute petite.
+papa|Elle a des points noirs.
+papa|Tu veux arroser un peu ?
+enfant-f|Oui.
+enfant-f|L'arrosoir est lourd.
+narrateur|En ce moment, Victorina arrose les fleurs.
+narrateur|L'eau fait un bruit doux.
+narrateur|Elle veut déplacer le pot de basilic.
+narrateur|Le pot bascule.
+narrateur|La terre s'étale.
+narrateur|Ça fait un tas brun sur la dalle.
+narrateur|Victorina sent son visage chaud.
+narrateur|Elle a le ventre serré.
+narrateur|Elle va vers papa.
+enfant-f|Papa, le pot est tombé.
+enfant-f|C'est moi.
+papa|Je t'écoute.
+papa|Merci de raconter.
+papa|On ramasse la terre.
+papa|Tu as fait du bon travail.
+papa|Tu veux la petite pelle ?
+enfant-f|Oui, papa.
+narrateur|Les mains sont un peu sales.
+narrateur|La terre revient dans le pot.
+narrateur|Le basilic se redresse, tout penché.
+papa|On se lave les mains, après ?
+enfant-f|Oui.
+narrateur|Plus tard, la cuisine sent le thym.
+narrateur|Un verre d'eau attend sur la table.
+narrateur|Victorina touche le verre.
+narrateur|Le verre tremble.
+narrateur|Victorina pense.
+narrateur|Je peux raconter à papa ou maman.
+narrateur|Maman essuie une assiette.
+enfant-f|Maman, j'ai touché le verre.
+enfant-f|Il a bougé.
+maman|Je t'écoute, Victorina.
+maman|Merci de raconter.
+maman|Raconter aide, au jardin et à la maison.
+maman|On raconte à papa ou maman.
+maman|Bravo.
+maman|C'est du bon travail.
+maman|Tu veux que je tienne le verre avec toi ?
+enfant-f|Oui, maman.
+narrateur|Le verre redevient calme.
+narrateur|Victorina souffle.
+papa|Les mains sont propres, maintenant ?
+enfant-f|Oui, papa.
+enfant-f|J'ai raconté deux fois.
+papa|Oui.
+papa|Chaque fois, on raconte.
+maman|Tu veux sentir le basilic, encore ?
+enfant-f|Oui.
+enfant-f|Il sent fort.
+narrateur|Victorina se lave un peu les doigts.
+narrateur|L'eau est froide, puis tiède.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>arrosoir,terre_pot</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1420,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Quelque chose est tombé. Que fait Sara ?</t>
+          <t>Quelque chose est tombé. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1576,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Quelque chose est tombé. Que fait Sara ?</t>
+          <t>narrateur|Quelque chose est tombé.
+narrateur|Que fait Victorina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1605,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara a raconté au jardin. Puis elle a raconté dans la cuisine. Papa et maman écoutent. Raconter, c'est possible à chaque fois.</t>
+          <t>Victorina a raconté au jardin. Puis elle a raconté dans la cuisine. Papa et maman écoutent. Raconter, c'est possible à chaque fois. Bravo, Victorina. J'ai raconté. Au jardin et ici. Oui. À papa ou à maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1749,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sara a raconté au jardin. Puis elle a raconté dans la cuisine. Papa et maman écoutent. Raconter, c'est possible à chaque fois.</t>
+          <t>narrateur|Victorina a raconté au jardin.
+narrateur|Puis elle a raconté dans la cuisine.
+papa|Papa et maman écoutent.
+maman|Raconter, c'est possible à chaque fois.
+papa|Bravo, Victorina.
+enfant-f|J'ai raconté.
+enfant-f|Au jardin et ici.
+maman|Oui.
+maman|À papa ou à maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le basilic est remis. Le verre est stable. Sara se lave les mains.</t>
+          <t>Le basilic est remis. Le verre est stable. Victorina se lave les mains. L'eau est tiède, hein ? Oui. Un peu savonneuse. Tu veux revoir la coccinelle, après ? Oui. Sur la feuille. Une goutte sèche encore sur la dalle.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,7 +1925,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le basilic est remis. Le verre est stable. Sara se lave les mains.</t>
+          <t>narrateur|Le basilic est remis.
+narrateur|Le verre est stable.
+narrateur|Victorina se lave les mains.
+maman|L'eau est tiède, hein ?
+enfant-f|Oui.
+enfant-f|Un peu savonneuse.
+papa|Tu veux revoir la coccinelle, après ?
+enfant-f|Oui.
+enfant-f|Sur la feuille.
+narrateur|Une goutte sèche encore sur la dalle.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1869,7 +1962,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté. Papa et maman ont écouté. Bravo. Tu as fait du bon travail. Le seau jaune reste près des fleurs. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,7 +2102,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai raconté.
+enfant-f|Papa et maman ont écouté.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le seau jaune reste près des fleurs.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2031,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2167,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir laisse une goutte sur les dalles. La goutte brille, puis s'étale. Le basilic sent fort, tout vert. Une coccinelle marche sur une feuille. La terre est sombre et un peu froide. Les mains de papa sont humides. Un seau jaune attend près des fleurs. Tu as vu la coccinelle, Victorina ? Oui, papa. Elle est toute petite. Elle a des points noirs. Tu veux arroser un peu ? Oui. L'arrosoir est lourd. En ce moment, Victorina arrose les fleurs. L'eau fait un bruit doux. Elle veut déplacer le pot de basilic. Le pot bascule. La terre s'étale. Ça fait un tas brun sur la dalle. Victorina sent son visage chaud. Elle a le ventre serré. Elle va vers papa. Papa, le pot est tombé. C'est moi. Je t'écoute. Merci de raconter. On ramasse la terre. Tu as fait du bon travail. Tu veux la petite pelle ? Oui, papa. Les mains sont un peu sales. La terre revient dans le pot. Le basilic se redresse, tout penché. On se lave les mains, après ? Oui. Plus tard, la cuisine sent le thym. Un verre d'eau attend sur la table. Victorina touche le verre. Le verre tremble. Victorina pense. Je peux raconter à papa ou maman. Maman essuie une assiette. Maman, j'ai touché le verre. Il a bougé. Je t'écoute, Victorina. Merci de raconter. Raconter aide, au jardin et à la maison. On raconte à papa ou maman. Bravo. C'est du bon travail. Tu veux que je tienne le verre avec toi ? Oui, maman. Le verre redevient calme. Victorina souffle. Les mains sont propres, maintenant ? Oui, papa. J'ai raconté deux fois. Oui. Chaque fois, on raconte. Tu veux sentir le basilic, encore ? Oui. Il sent fort. Victorina se lave un peu les doigts. L'eau est froide, puis tiède.</t>
+          <t>L'arrosoir laisse une goutte sur les dalles. La goutte brille, puis s'étale. Le basilic sent fort, tout vert. Une coccinelle marche sur une feuille. La terre est sombre et un peu froide. Les mains de papa sont humides. Un seau jaune attend près des fleurs. Tu as vu la coccinelle, Victorina ? Oui, papa. Elle est toute petite. Elle a des points noirs. Tu veux arroser un peu ? Oui. L'arrosoir est lourd. En ce moment, Victorina arrose les fleurs. L'eau fait un bruit doux. Elle veut déplacer le pot de basilic. Le pot bascule. La terre s'étale. Ça fait un tas brun sur la dalle. Victorina sent son visage chaud. Elle a le ventre serré. Elle va vers papa. Papa, le pot est tombé. C'est moi. Je t'écoute. Merci de raconter. On ramasse la terre. Tu veux la petite pelle ? Oui, papa. Les mains sont un peu sales. La terre revient dans le pot. Le basilic se redresse, tout penché. On se lave les mains, après ? Oui. Plus tard, la cuisine sent le thym. Un verre d'eau attend sur la table. Victorina touche le verre. Le verre tremble. Victorina pense. Je peux raconter à papa ou maman. Maman essuie une assiette. Maman, j'ai touché le verre. Il a bougé. Je t'écoute, Victorina. Merci de raconter. Raconter aide, au jardin et à la maison. On raconte à papa ou maman. Bravo. Tu veux que je tienne le verre avec toi ? Oui, maman. Le verre redevient calme. Victorina souffle. Les mains sont propres, maintenant ? Oui, papa. J'ai raconté deux fois. Oui. Chaque fois, on raconte. Tu veux sentir le basilic, encore ? Oui. Il sent fort. Victorina se lave un peu les doigts. L'eau est froide, puis tiède.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara est dans le jardin avec papa. Elle arrose les fleurs. L'arrosoir est lourd. L'eau fait un bruit doux. Le pot de basilic bascule. La terre s'étale. Sara sent son visage chaud. Elle va vers papa. Sara dit : papa, le pot est tombé. C'est moi. Papa l'écoute. Papa dit : merci de &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. On ramasse la terre. Les mains sont un peu sales. Plus tard, dans la cuisine, Sara touche un verre. Le verre tremble. Sara pense : je peux raconter à papa ou maman. Elle dit : maman, j'ai touché le verre. Il a bougé. Maman dit : merci Sara. Raconter aide, au jardin et à la maison. Papa et maman sont là.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrosoir laisse une goutte sur les dalles. La goutte brille, puis s'étale. Le basilic sent fort, tout vert. Une coccinelle marche sur une feuille. La terre est sombre et un peu froide. Les mains de papa sont humides. Un seau jaune attend près des fleurs. Tu as vu la coccinelle, Victorina ? Oui, papa. Elle est toute petite. Elle a des points noirs. Tu veux arroser un peu ? Oui. L'arrosoir est lourd. En ce moment, Victorina arrose les fleurs. L'eau fait un bruit doux. Elle veut déplacer le pot de basilic. Le pot bascule. La terre s'étale. Ça fait un tas brun sur la dalle. Victorina sent son visage chaud. Elle a le ventre serré. Elle va vers papa. Papa, le pot est tombé. C'est moi. Je t'écoute. Merci de raconter. On ramasse la terre. Tu veux la petite pelle ? Oui, papa. Les mains sont un peu sales. La terre revient dans le pot. Le basilic se redresse, tout penché. On se lave les mains, après ? Oui. Plus tard, la cuisine sent le thym. Un verre d'eau attend sur la table. Victorina touche le verre. Le verre tremble. Victorina pense. Je peux raconter à papa ou maman. Maman essuie une assiette. Maman, j'ai touché le verre. Il a bougé. Je t'écoute, Victorina. Merci de raconter. Raconter aide, au jardin et à la maison. On raconte à papa ou maman. Bravo. Tu veux que je tienne le verre avec toi ? Oui, maman. Le verre redevient calme. Victorina souffle. Les mains sont propres, maintenant ? Oui, papa. J'ai raconté deux fois. Oui. Chaque fois, on raconte. Tu veux sentir le basilic, encore ? Oui. Il sent fort. Victorina se lave un peu les doigts. L'eau est froide, puis tiède.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1352,7 +1352,6 @@
 papa|Je t'écoute.
 papa|Merci de raconter.
 papa|On ramasse la terre.
-papa|Tu as fait du bon travail.
 papa|Tu veux la petite pelle ?
 enfant-f|Oui, papa.
 narrateur|Les mains sont un peu sales.
@@ -1374,7 +1373,6 @@
 maman|Raconter aide, au jardin et à la maison.
 maman|On raconte à papa ou maman.
 maman|Bravo.
-maman|C'est du bon travail.
 maman|Tu veux que je tienne le verre avec toi ?
 enfant-f|Oui, maman.
 narrateur|Le verre redevient calme.
@@ -1425,7 +1423,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Quelque chose est tombé. Que fait Sara ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Quelque chose est tombé. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1580,7 +1578,6 @@
 narrateur|Que fait Victorina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1610,7 +1607,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara a raconté au jardin. Puis elle a raconté dans la cuisine. Papa et maman écoutent. &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;, c'est possible à chaque fois.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a raconté au jardin. Puis elle a raconté dans la cuisine. Papa et maman écoutent. Raconter, c'est possible à chaque fois. Bravo, Victorina. J'ai raconté. Au jardin et ici. Oui. À papa ou à maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1760,7 +1757,6 @@
 maman|À papa ou à maman.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1790,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le basilic est remis. Le verre est stable. Sara se lave les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le basilic est remis. Le verre est stable. Victorina se lave les mains. L'eau est tiède, hein ? Oui. Un peu savonneuse. Tu veux revoir la coccinelle, après ? Oui. Sur la feuille. Une goutte sèche encore sur la dalle.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1937,7 +1933,6 @@
 narrateur|Une goutte sèche encore sur la dalle.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1962,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. Papa et maman ont écouté. Bravo. Tu as fait du bon travail. Le seau jaune reste près des fleurs. L'histoire est finie.</t>
+          <t>J'ai raconté. Papa et maman ont écouté. Bravo. Le seau jaune reste près des fleurs.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté. Papa et maman ont écouté. Bravo. Le seau jaune reste près des fleurs.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2105,12 +2100,9 @@
           <t>enfant-f|J'ai raconté.
 enfant-f|Papa et maman ont écouté.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le seau jaune reste près des fleurs.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le seau jaune reste près des fleurs.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2129,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2174,6 +2166,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sara, papa, maman</t>
+          <t>Victorina, papa, maman</t>
         </is>
       </c>
     </row>
